--- a/library-template/home-library-inventory.xlsx
+++ b/library-template/home-library-inventory.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Start here" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My library'!$A$1:$J$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My library'!$A$1:$N$500</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,11 @@
     <font>
       <b val="1"/>
       <color rgb="00F2EEE8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A120A"/>
       <sz val="11"/>
     </font>
     <font>
@@ -54,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D75340"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A4A056"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -97,14 +107,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J500"/>
+  <dimension ref="A1:N500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -484,7 +497,11 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -535,12 +552,32 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Acquired</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Date read</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>My notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>9780141439518</t>
         </is>
@@ -581,10 +618,32 @@
           <t>Living room</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-10</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Reread every few winters.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>9780547928227</t>
         </is>
@@ -625,14 +684,32 @@
           <t>Living room</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Gift from Dad</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2019-12-25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-06</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Read aloud over Christmas break.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>9780451524935</t>
         </is>
@@ -673,10 +750,28 @@
           <t>Office</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>2021-03-15</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>9781400033416</t>
         </is>
@@ -717,1500 +812,2502 @@
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Book club pick, May 2024</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Currently reading</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Book club pick for May.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
+      <c r="A6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
+      <c r="A7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
+      <c r="A8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
+      <c r="A9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
+      <c r="A10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
+      <c r="A11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
+      <c r="A12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
+      <c r="A13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n"/>
+      <c r="A14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n"/>
+      <c r="A16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n"/>
+      <c r="A17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n"/>
+      <c r="A19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n"/>
+      <c r="A28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n"/>
+      <c r="A29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n"/>
+      <c r="A30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n"/>
+      <c r="A31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n"/>
+      <c r="A32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n"/>
+      <c r="A33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n"/>
+      <c r="A34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n"/>
+      <c r="A35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n"/>
+      <c r="A36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n"/>
+      <c r="A37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n"/>
+      <c r="A38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n"/>
+      <c r="A39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n"/>
+      <c r="A40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n"/>
+      <c r="A41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n"/>
+      <c r="A42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n"/>
+      <c r="A43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n"/>
+      <c r="A44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n"/>
+      <c r="A45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n"/>
+      <c r="A46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n"/>
+      <c r="A47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n"/>
+      <c r="A48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n"/>
+      <c r="A49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n"/>
+      <c r="A50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n"/>
+      <c r="A51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n"/>
+      <c r="A52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n"/>
+      <c r="A53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n"/>
+      <c r="A54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n"/>
+      <c r="A55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n"/>
+      <c r="A56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n"/>
+      <c r="A57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n"/>
+      <c r="A58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n"/>
+      <c r="A59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n"/>
+      <c r="A60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n"/>
+      <c r="A61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n"/>
+      <c r="A62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n"/>
+      <c r="A63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n"/>
+      <c r="A64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n"/>
+      <c r="A65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n"/>
+      <c r="A66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n"/>
+      <c r="A67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n"/>
+      <c r="A68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n"/>
+      <c r="A69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n"/>
+      <c r="A70" s="4" t="n"/>
+      <c r="J70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n"/>
+      <c r="A71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n"/>
+      <c r="A72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n"/>
+      <c r="A73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n"/>
+      <c r="A74" s="4" t="n"/>
+      <c r="J74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n"/>
+      <c r="A75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n"/>
+      <c r="A76" s="4" t="n"/>
+      <c r="J76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n"/>
+      <c r="A77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n"/>
+      <c r="A78" s="4" t="n"/>
+      <c r="J78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n"/>
+      <c r="A79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n"/>
+      <c r="A80" s="4" t="n"/>
+      <c r="J80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n"/>
+      <c r="A81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n"/>
+      <c r="A82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n"/>
+      <c r="A83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n"/>
+      <c r="A84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n"/>
+      <c r="A85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n"/>
+      <c r="A86" s="4" t="n"/>
+      <c r="J86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n"/>
+      <c r="A87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n"/>
+      <c r="A88" s="4" t="n"/>
+      <c r="J88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n"/>
+      <c r="A89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n"/>
+      <c r="A90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n"/>
+      <c r="A91" s="4" t="n"/>
+      <c r="J91" s="4" t="n"/>
+      <c r="M91" s="4" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n"/>
+      <c r="A92" s="4" t="n"/>
+      <c r="J92" s="4" t="n"/>
+      <c r="M92" s="4" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n"/>
+      <c r="A93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n"/>
+      <c r="A94" s="4" t="n"/>
+      <c r="J94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n"/>
+      <c r="A95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n"/>
+      <c r="A96" s="4" t="n"/>
+      <c r="J96" s="4" t="n"/>
+      <c r="M96" s="4" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n"/>
+      <c r="A97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n"/>
+      <c r="A98" s="4" t="n"/>
+      <c r="J98" s="4" t="n"/>
+      <c r="M98" s="4" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n"/>
+      <c r="A99" s="4" t="n"/>
+      <c r="J99" s="4" t="n"/>
+      <c r="M99" s="4" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n"/>
+      <c r="A100" s="4" t="n"/>
+      <c r="J100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n"/>
+      <c r="A101" s="4" t="n"/>
+      <c r="J101" s="4" t="n"/>
+      <c r="M101" s="4" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n"/>
+      <c r="A102" s="4" t="n"/>
+      <c r="J102" s="4" t="n"/>
+      <c r="M102" s="4" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n"/>
+      <c r="A103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n"/>
+      <c r="A104" s="4" t="n"/>
+      <c r="J104" s="4" t="n"/>
+      <c r="M104" s="4" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n"/>
+      <c r="A105" s="4" t="n"/>
+      <c r="J105" s="4" t="n"/>
+      <c r="M105" s="4" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n"/>
+      <c r="A106" s="4" t="n"/>
+      <c r="J106" s="4" t="n"/>
+      <c r="M106" s="4" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n"/>
+      <c r="A107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="M107" s="4" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n"/>
+      <c r="A108" s="4" t="n"/>
+      <c r="J108" s="4" t="n"/>
+      <c r="M108" s="4" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n"/>
+      <c r="A109" s="4" t="n"/>
+      <c r="J109" s="4" t="n"/>
+      <c r="M109" s="4" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n"/>
+      <c r="A110" s="4" t="n"/>
+      <c r="J110" s="4" t="n"/>
+      <c r="M110" s="4" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n"/>
+      <c r="A111" s="4" t="n"/>
+      <c r="J111" s="4" t="n"/>
+      <c r="M111" s="4" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n"/>
+      <c r="A112" s="4" t="n"/>
+      <c r="J112" s="4" t="n"/>
+      <c r="M112" s="4" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n"/>
+      <c r="A113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n"/>
+      <c r="A114" s="4" t="n"/>
+      <c r="J114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n"/>
+      <c r="A115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n"/>
+      <c r="A116" s="4" t="n"/>
+      <c r="J116" s="4" t="n"/>
+      <c r="M116" s="4" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n"/>
+      <c r="A117" s="4" t="n"/>
+      <c r="J117" s="4" t="n"/>
+      <c r="M117" s="4" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n"/>
+      <c r="A118" s="4" t="n"/>
+      <c r="J118" s="4" t="n"/>
+      <c r="M118" s="4" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n"/>
+      <c r="A119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
+      <c r="M119" s="4" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n"/>
+      <c r="A120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n"/>
+      <c r="A121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n"/>
+      <c r="A122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
+      <c r="M122" s="4" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n"/>
+      <c r="A123" s="4" t="n"/>
+      <c r="J123" s="4" t="n"/>
+      <c r="M123" s="4" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n"/>
+      <c r="A124" s="4" t="n"/>
+      <c r="J124" s="4" t="n"/>
+      <c r="M124" s="4" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n"/>
+      <c r="A125" s="4" t="n"/>
+      <c r="J125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n"/>
+      <c r="A126" s="4" t="n"/>
+      <c r="J126" s="4" t="n"/>
+      <c r="M126" s="4" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n"/>
+      <c r="A127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n"/>
+      <c r="A128" s="4" t="n"/>
+      <c r="J128" s="4" t="n"/>
+      <c r="M128" s="4" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n"/>
+      <c r="A129" s="4" t="n"/>
+      <c r="J129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n"/>
+      <c r="A130" s="4" t="n"/>
+      <c r="J130" s="4" t="n"/>
+      <c r="M130" s="4" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n"/>
+      <c r="A131" s="4" t="n"/>
+      <c r="J131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n"/>
+      <c r="A132" s="4" t="n"/>
+      <c r="J132" s="4" t="n"/>
+      <c r="M132" s="4" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n"/>
+      <c r="A133" s="4" t="n"/>
+      <c r="J133" s="4" t="n"/>
+      <c r="M133" s="4" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n"/>
+      <c r="A134" s="4" t="n"/>
+      <c r="J134" s="4" t="n"/>
+      <c r="M134" s="4" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n"/>
+      <c r="A135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n"/>
+      <c r="A136" s="4" t="n"/>
+      <c r="J136" s="4" t="n"/>
+      <c r="M136" s="4" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n"/>
+      <c r="A137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n"/>
+      <c r="A138" s="4" t="n"/>
+      <c r="J138" s="4" t="n"/>
+      <c r="M138" s="4" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n"/>
+      <c r="A139" s="4" t="n"/>
+      <c r="J139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n"/>
+      <c r="A140" s="4" t="n"/>
+      <c r="J140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n"/>
+      <c r="A141" s="4" t="n"/>
+      <c r="J141" s="4" t="n"/>
+      <c r="M141" s="4" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n"/>
+      <c r="A142" s="4" t="n"/>
+      <c r="J142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n"/>
+      <c r="A143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="M143" s="4" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n"/>
+      <c r="A144" s="4" t="n"/>
+      <c r="J144" s="4" t="n"/>
+      <c r="M144" s="4" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n"/>
+      <c r="A145" s="4" t="n"/>
+      <c r="J145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n"/>
+      <c r="A146" s="4" t="n"/>
+      <c r="J146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n"/>
+      <c r="A147" s="4" t="n"/>
+      <c r="J147" s="4" t="n"/>
+      <c r="M147" s="4" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n"/>
+      <c r="A148" s="4" t="n"/>
+      <c r="J148" s="4" t="n"/>
+      <c r="M148" s="4" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n"/>
+      <c r="A149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n"/>
+      <c r="A150" s="4" t="n"/>
+      <c r="J150" s="4" t="n"/>
+      <c r="M150" s="4" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n"/>
+      <c r="A151" s="4" t="n"/>
+      <c r="J151" s="4" t="n"/>
+      <c r="M151" s="4" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="n"/>
+      <c r="A152" s="4" t="n"/>
+      <c r="J152" s="4" t="n"/>
+      <c r="M152" s="4" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="n"/>
+      <c r="A153" s="4" t="n"/>
+      <c r="J153" s="4" t="n"/>
+      <c r="M153" s="4" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n"/>
+      <c r="A154" s="4" t="n"/>
+      <c r="J154" s="4" t="n"/>
+      <c r="M154" s="4" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n"/>
+      <c r="A155" s="4" t="n"/>
+      <c r="J155" s="4" t="n"/>
+      <c r="M155" s="4" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n"/>
+      <c r="A156" s="4" t="n"/>
+      <c r="J156" s="4" t="n"/>
+      <c r="M156" s="4" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n"/>
+      <c r="A157" s="4" t="n"/>
+      <c r="J157" s="4" t="n"/>
+      <c r="M157" s="4" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n"/>
+      <c r="A158" s="4" t="n"/>
+      <c r="J158" s="4" t="n"/>
+      <c r="M158" s="4" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="n"/>
+      <c r="A159" s="4" t="n"/>
+      <c r="J159" s="4" t="n"/>
+      <c r="M159" s="4" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="n"/>
+      <c r="A160" s="4" t="n"/>
+      <c r="J160" s="4" t="n"/>
+      <c r="M160" s="4" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n"/>
+      <c r="A161" s="4" t="n"/>
+      <c r="J161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n"/>
+      <c r="A162" s="4" t="n"/>
+      <c r="J162" s="4" t="n"/>
+      <c r="M162" s="4" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n"/>
+      <c r="A163" s="4" t="n"/>
+      <c r="J163" s="4" t="n"/>
+      <c r="M163" s="4" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n"/>
+      <c r="A164" s="4" t="n"/>
+      <c r="J164" s="4" t="n"/>
+      <c r="M164" s="4" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n"/>
+      <c r="A165" s="4" t="n"/>
+      <c r="J165" s="4" t="n"/>
+      <c r="M165" s="4" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n"/>
+      <c r="A166" s="4" t="n"/>
+      <c r="J166" s="4" t="n"/>
+      <c r="M166" s="4" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n"/>
+      <c r="A167" s="4" t="n"/>
+      <c r="J167" s="4" t="n"/>
+      <c r="M167" s="4" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n"/>
+      <c r="A168" s="4" t="n"/>
+      <c r="J168" s="4" t="n"/>
+      <c r="M168" s="4" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n"/>
+      <c r="A169" s="4" t="n"/>
+      <c r="J169" s="4" t="n"/>
+      <c r="M169" s="4" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n"/>
+      <c r="A170" s="4" t="n"/>
+      <c r="J170" s="4" t="n"/>
+      <c r="M170" s="4" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n"/>
+      <c r="A171" s="4" t="n"/>
+      <c r="J171" s="4" t="n"/>
+      <c r="M171" s="4" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n"/>
+      <c r="A172" s="4" t="n"/>
+      <c r="J172" s="4" t="n"/>
+      <c r="M172" s="4" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n"/>
+      <c r="A173" s="4" t="n"/>
+      <c r="J173" s="4" t="n"/>
+      <c r="M173" s="4" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n"/>
+      <c r="A174" s="4" t="n"/>
+      <c r="J174" s="4" t="n"/>
+      <c r="M174" s="4" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n"/>
+      <c r="A175" s="4" t="n"/>
+      <c r="J175" s="4" t="n"/>
+      <c r="M175" s="4" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n"/>
+      <c r="A176" s="4" t="n"/>
+      <c r="J176" s="4" t="n"/>
+      <c r="M176" s="4" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n"/>
+      <c r="A177" s="4" t="n"/>
+      <c r="J177" s="4" t="n"/>
+      <c r="M177" s="4" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n"/>
+      <c r="A178" s="4" t="n"/>
+      <c r="J178" s="4" t="n"/>
+      <c r="M178" s="4" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n"/>
+      <c r="A179" s="4" t="n"/>
+      <c r="J179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n"/>
+      <c r="A180" s="4" t="n"/>
+      <c r="J180" s="4" t="n"/>
+      <c r="M180" s="4" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n"/>
+      <c r="A181" s="4" t="n"/>
+      <c r="J181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n"/>
+      <c r="A182" s="4" t="n"/>
+      <c r="J182" s="4" t="n"/>
+      <c r="M182" s="4" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n"/>
+      <c r="A183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
+      <c r="M183" s="4" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n"/>
+      <c r="A184" s="4" t="n"/>
+      <c r="J184" s="4" t="n"/>
+      <c r="M184" s="4" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n"/>
+      <c r="A185" s="4" t="n"/>
+      <c r="J185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n"/>
+      <c r="A186" s="4" t="n"/>
+      <c r="J186" s="4" t="n"/>
+      <c r="M186" s="4" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n"/>
+      <c r="A187" s="4" t="n"/>
+      <c r="J187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="n"/>
+      <c r="A188" s="4" t="n"/>
+      <c r="J188" s="4" t="n"/>
+      <c r="M188" s="4" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="n"/>
+      <c r="A189" s="4" t="n"/>
+      <c r="J189" s="4" t="n"/>
+      <c r="M189" s="4" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n"/>
+      <c r="A190" s="4" t="n"/>
+      <c r="J190" s="4" t="n"/>
+      <c r="M190" s="4" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="n"/>
+      <c r="A191" s="4" t="n"/>
+      <c r="J191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="n"/>
+      <c r="A192" s="4" t="n"/>
+      <c r="J192" s="4" t="n"/>
+      <c r="M192" s="4" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n"/>
+      <c r="A193" s="4" t="n"/>
+      <c r="J193" s="4" t="n"/>
+      <c r="M193" s="4" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n"/>
+      <c r="A194" s="4" t="n"/>
+      <c r="J194" s="4" t="n"/>
+      <c r="M194" s="4" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="n"/>
+      <c r="A195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n"/>
+      <c r="A196" s="4" t="n"/>
+      <c r="J196" s="4" t="n"/>
+      <c r="M196" s="4" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="n"/>
+      <c r="A197" s="4" t="n"/>
+      <c r="J197" s="4" t="n"/>
+      <c r="M197" s="4" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="n"/>
+      <c r="A198" s="4" t="n"/>
+      <c r="J198" s="4" t="n"/>
+      <c r="M198" s="4" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n"/>
+      <c r="A199" s="4" t="n"/>
+      <c r="J199" s="4" t="n"/>
+      <c r="M199" s="4" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="n"/>
+      <c r="A200" s="4" t="n"/>
+      <c r="J200" s="4" t="n"/>
+      <c r="M200" s="4" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="n"/>
+      <c r="A201" s="4" t="n"/>
+      <c r="J201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n"/>
+      <c r="A202" s="4" t="n"/>
+      <c r="J202" s="4" t="n"/>
+      <c r="M202" s="4" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="n"/>
+      <c r="A203" s="4" t="n"/>
+      <c r="J203" s="4" t="n"/>
+      <c r="M203" s="4" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n"/>
+      <c r="A204" s="4" t="n"/>
+      <c r="J204" s="4" t="n"/>
+      <c r="M204" s="4" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n"/>
+      <c r="A205" s="4" t="n"/>
+      <c r="J205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="n"/>
+      <c r="A206" s="4" t="n"/>
+      <c r="J206" s="4" t="n"/>
+      <c r="M206" s="4" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="n"/>
+      <c r="A207" s="4" t="n"/>
+      <c r="J207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n"/>
+      <c r="A208" s="4" t="n"/>
+      <c r="J208" s="4" t="n"/>
+      <c r="M208" s="4" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="n"/>
+      <c r="A209" s="4" t="n"/>
+      <c r="J209" s="4" t="n"/>
+      <c r="M209" s="4" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n"/>
+      <c r="A210" s="4" t="n"/>
+      <c r="J210" s="4" t="n"/>
+      <c r="M210" s="4" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n"/>
+      <c r="A211" s="4" t="n"/>
+      <c r="J211" s="4" t="n"/>
+      <c r="M211" s="4" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="n"/>
+      <c r="A212" s="4" t="n"/>
+      <c r="J212" s="4" t="n"/>
+      <c r="M212" s="4" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="n"/>
+      <c r="A213" s="4" t="n"/>
+      <c r="J213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="n"/>
+      <c r="A214" s="4" t="n"/>
+      <c r="J214" s="4" t="n"/>
+      <c r="M214" s="4" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="n"/>
+      <c r="A215" s="4" t="n"/>
+      <c r="J215" s="4" t="n"/>
+      <c r="M215" s="4" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="n"/>
+      <c r="A216" s="4" t="n"/>
+      <c r="J216" s="4" t="n"/>
+      <c r="M216" s="4" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n"/>
+      <c r="A217" s="4" t="n"/>
+      <c r="J217" s="4" t="n"/>
+      <c r="M217" s="4" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="n"/>
+      <c r="A218" s="4" t="n"/>
+      <c r="J218" s="4" t="n"/>
+      <c r="M218" s="4" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="n"/>
+      <c r="A219" s="4" t="n"/>
+      <c r="J219" s="4" t="n"/>
+      <c r="M219" s="4" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="n"/>
+      <c r="A220" s="4" t="n"/>
+      <c r="J220" s="4" t="n"/>
+      <c r="M220" s="4" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="n"/>
+      <c r="A221" s="4" t="n"/>
+      <c r="J221" s="4" t="n"/>
+      <c r="M221" s="4" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="n"/>
+      <c r="A222" s="4" t="n"/>
+      <c r="J222" s="4" t="n"/>
+      <c r="M222" s="4" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="n"/>
+      <c r="A223" s="4" t="n"/>
+      <c r="J223" s="4" t="n"/>
+      <c r="M223" s="4" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="n"/>
+      <c r="A224" s="4" t="n"/>
+      <c r="J224" s="4" t="n"/>
+      <c r="M224" s="4" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="n"/>
+      <c r="A225" s="4" t="n"/>
+      <c r="J225" s="4" t="n"/>
+      <c r="M225" s="4" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="n"/>
+      <c r="A226" s="4" t="n"/>
+      <c r="J226" s="4" t="n"/>
+      <c r="M226" s="4" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="n"/>
+      <c r="A227" s="4" t="n"/>
+      <c r="J227" s="4" t="n"/>
+      <c r="M227" s="4" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="n"/>
+      <c r="A228" s="4" t="n"/>
+      <c r="J228" s="4" t="n"/>
+      <c r="M228" s="4" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="n"/>
+      <c r="A229" s="4" t="n"/>
+      <c r="J229" s="4" t="n"/>
+      <c r="M229" s="4" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="n"/>
+      <c r="A230" s="4" t="n"/>
+      <c r="J230" s="4" t="n"/>
+      <c r="M230" s="4" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="n"/>
+      <c r="A231" s="4" t="n"/>
+      <c r="J231" s="4" t="n"/>
+      <c r="M231" s="4" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="n"/>
+      <c r="A232" s="4" t="n"/>
+      <c r="J232" s="4" t="n"/>
+      <c r="M232" s="4" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="n"/>
+      <c r="A233" s="4" t="n"/>
+      <c r="J233" s="4" t="n"/>
+      <c r="M233" s="4" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="n"/>
+      <c r="A234" s="4" t="n"/>
+      <c r="J234" s="4" t="n"/>
+      <c r="M234" s="4" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="n"/>
+      <c r="A235" s="4" t="n"/>
+      <c r="J235" s="4" t="n"/>
+      <c r="M235" s="4" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="n"/>
+      <c r="A236" s="4" t="n"/>
+      <c r="J236" s="4" t="n"/>
+      <c r="M236" s="4" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="3" t="n"/>
+      <c r="A237" s="4" t="n"/>
+      <c r="J237" s="4" t="n"/>
+      <c r="M237" s="4" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="n"/>
+      <c r="A238" s="4" t="n"/>
+      <c r="J238" s="4" t="n"/>
+      <c r="M238" s="4" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="n"/>
+      <c r="A239" s="4" t="n"/>
+      <c r="J239" s="4" t="n"/>
+      <c r="M239" s="4" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="n"/>
+      <c r="A240" s="4" t="n"/>
+      <c r="J240" s="4" t="n"/>
+      <c r="M240" s="4" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="n"/>
+      <c r="A241" s="4" t="n"/>
+      <c r="J241" s="4" t="n"/>
+      <c r="M241" s="4" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="n"/>
+      <c r="A242" s="4" t="n"/>
+      <c r="J242" s="4" t="n"/>
+      <c r="M242" s="4" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="n"/>
+      <c r="A243" s="4" t="n"/>
+      <c r="J243" s="4" t="n"/>
+      <c r="M243" s="4" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="n"/>
+      <c r="A244" s="4" t="n"/>
+      <c r="J244" s="4" t="n"/>
+      <c r="M244" s="4" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="n"/>
+      <c r="A245" s="4" t="n"/>
+      <c r="J245" s="4" t="n"/>
+      <c r="M245" s="4" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="n"/>
+      <c r="A246" s="4" t="n"/>
+      <c r="J246" s="4" t="n"/>
+      <c r="M246" s="4" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="n"/>
+      <c r="A247" s="4" t="n"/>
+      <c r="J247" s="4" t="n"/>
+      <c r="M247" s="4" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="n"/>
+      <c r="A248" s="4" t="n"/>
+      <c r="J248" s="4" t="n"/>
+      <c r="M248" s="4" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="n"/>
+      <c r="A249" s="4" t="n"/>
+      <c r="J249" s="4" t="n"/>
+      <c r="M249" s="4" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="n"/>
+      <c r="A250" s="4" t="n"/>
+      <c r="J250" s="4" t="n"/>
+      <c r="M250" s="4" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="n"/>
+      <c r="A251" s="4" t="n"/>
+      <c r="J251" s="4" t="n"/>
+      <c r="M251" s="4" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="n"/>
+      <c r="A252" s="4" t="n"/>
+      <c r="J252" s="4" t="n"/>
+      <c r="M252" s="4" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="n"/>
+      <c r="A253" s="4" t="n"/>
+      <c r="J253" s="4" t="n"/>
+      <c r="M253" s="4" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="n"/>
+      <c r="A254" s="4" t="n"/>
+      <c r="J254" s="4" t="n"/>
+      <c r="M254" s="4" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="n"/>
+      <c r="A255" s="4" t="n"/>
+      <c r="J255" s="4" t="n"/>
+      <c r="M255" s="4" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="n"/>
+      <c r="A256" s="4" t="n"/>
+      <c r="J256" s="4" t="n"/>
+      <c r="M256" s="4" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="n"/>
+      <c r="A257" s="4" t="n"/>
+      <c r="J257" s="4" t="n"/>
+      <c r="M257" s="4" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="n"/>
+      <c r="A258" s="4" t="n"/>
+      <c r="J258" s="4" t="n"/>
+      <c r="M258" s="4" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="n"/>
+      <c r="A259" s="4" t="n"/>
+      <c r="J259" s="4" t="n"/>
+      <c r="M259" s="4" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="n"/>
+      <c r="A260" s="4" t="n"/>
+      <c r="J260" s="4" t="n"/>
+      <c r="M260" s="4" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="n"/>
+      <c r="A261" s="4" t="n"/>
+      <c r="J261" s="4" t="n"/>
+      <c r="M261" s="4" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="n"/>
+      <c r="A262" s="4" t="n"/>
+      <c r="J262" s="4" t="n"/>
+      <c r="M262" s="4" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="n"/>
+      <c r="A263" s="4" t="n"/>
+      <c r="J263" s="4" t="n"/>
+      <c r="M263" s="4" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="n"/>
+      <c r="A264" s="4" t="n"/>
+      <c r="J264" s="4" t="n"/>
+      <c r="M264" s="4" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="n"/>
+      <c r="A265" s="4" t="n"/>
+      <c r="J265" s="4" t="n"/>
+      <c r="M265" s="4" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="n"/>
+      <c r="A266" s="4" t="n"/>
+      <c r="J266" s="4" t="n"/>
+      <c r="M266" s="4" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="n"/>
+      <c r="A267" s="4" t="n"/>
+      <c r="J267" s="4" t="n"/>
+      <c r="M267" s="4" t="n"/>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="n"/>
+      <c r="A268" s="4" t="n"/>
+      <c r="J268" s="4" t="n"/>
+      <c r="M268" s="4" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="n"/>
+      <c r="A269" s="4" t="n"/>
+      <c r="J269" s="4" t="n"/>
+      <c r="M269" s="4" t="n"/>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="n"/>
+      <c r="A270" s="4" t="n"/>
+      <c r="J270" s="4" t="n"/>
+      <c r="M270" s="4" t="n"/>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="n"/>
+      <c r="A271" s="4" t="n"/>
+      <c r="J271" s="4" t="n"/>
+      <c r="M271" s="4" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="n"/>
+      <c r="A272" s="4" t="n"/>
+      <c r="J272" s="4" t="n"/>
+      <c r="M272" s="4" t="n"/>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="n"/>
+      <c r="A273" s="4" t="n"/>
+      <c r="J273" s="4" t="n"/>
+      <c r="M273" s="4" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="n"/>
+      <c r="A274" s="4" t="n"/>
+      <c r="J274" s="4" t="n"/>
+      <c r="M274" s="4" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="n"/>
+      <c r="A275" s="4" t="n"/>
+      <c r="J275" s="4" t="n"/>
+      <c r="M275" s="4" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="n"/>
+      <c r="A276" s="4" t="n"/>
+      <c r="J276" s="4" t="n"/>
+      <c r="M276" s="4" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="n"/>
+      <c r="A277" s="4" t="n"/>
+      <c r="J277" s="4" t="n"/>
+      <c r="M277" s="4" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="n"/>
+      <c r="A278" s="4" t="n"/>
+      <c r="J278" s="4" t="n"/>
+      <c r="M278" s="4" t="n"/>
     </row>
     <row r="279">
-      <c r="A279" s="3" t="n"/>
+      <c r="A279" s="4" t="n"/>
+      <c r="J279" s="4" t="n"/>
+      <c r="M279" s="4" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="n"/>
+      <c r="A280" s="4" t="n"/>
+      <c r="J280" s="4" t="n"/>
+      <c r="M280" s="4" t="n"/>
     </row>
     <row r="281">
-      <c r="A281" s="3" t="n"/>
+      <c r="A281" s="4" t="n"/>
+      <c r="J281" s="4" t="n"/>
+      <c r="M281" s="4" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="n"/>
+      <c r="A282" s="4" t="n"/>
+      <c r="J282" s="4" t="n"/>
+      <c r="M282" s="4" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="3" t="n"/>
+      <c r="A283" s="4" t="n"/>
+      <c r="J283" s="4" t="n"/>
+      <c r="M283" s="4" t="n"/>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="n"/>
+      <c r="A284" s="4" t="n"/>
+      <c r="J284" s="4" t="n"/>
+      <c r="M284" s="4" t="n"/>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="n"/>
+      <c r="A285" s="4" t="n"/>
+      <c r="J285" s="4" t="n"/>
+      <c r="M285" s="4" t="n"/>
     </row>
     <row r="286">
-      <c r="A286" s="3" t="n"/>
+      <c r="A286" s="4" t="n"/>
+      <c r="J286" s="4" t="n"/>
+      <c r="M286" s="4" t="n"/>
     </row>
     <row r="287">
-      <c r="A287" s="3" t="n"/>
+      <c r="A287" s="4" t="n"/>
+      <c r="J287" s="4" t="n"/>
+      <c r="M287" s="4" t="n"/>
     </row>
     <row r="288">
-      <c r="A288" s="3" t="n"/>
+      <c r="A288" s="4" t="n"/>
+      <c r="J288" s="4" t="n"/>
+      <c r="M288" s="4" t="n"/>
     </row>
     <row r="289">
-      <c r="A289" s="3" t="n"/>
+      <c r="A289" s="4" t="n"/>
+      <c r="J289" s="4" t="n"/>
+      <c r="M289" s="4" t="n"/>
     </row>
     <row r="290">
-      <c r="A290" s="3" t="n"/>
+      <c r="A290" s="4" t="n"/>
+      <c r="J290" s="4" t="n"/>
+      <c r="M290" s="4" t="n"/>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="n"/>
+      <c r="A291" s="4" t="n"/>
+      <c r="J291" s="4" t="n"/>
+      <c r="M291" s="4" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="3" t="n"/>
+      <c r="A292" s="4" t="n"/>
+      <c r="J292" s="4" t="n"/>
+      <c r="M292" s="4" t="n"/>
     </row>
     <row r="293">
-      <c r="A293" s="3" t="n"/>
+      <c r="A293" s="4" t="n"/>
+      <c r="J293" s="4" t="n"/>
+      <c r="M293" s="4" t="n"/>
     </row>
     <row r="294">
-      <c r="A294" s="3" t="n"/>
+      <c r="A294" s="4" t="n"/>
+      <c r="J294" s="4" t="n"/>
+      <c r="M294" s="4" t="n"/>
     </row>
     <row r="295">
-      <c r="A295" s="3" t="n"/>
+      <c r="A295" s="4" t="n"/>
+      <c r="J295" s="4" t="n"/>
+      <c r="M295" s="4" t="n"/>
     </row>
     <row r="296">
-      <c r="A296" s="3" t="n"/>
+      <c r="A296" s="4" t="n"/>
+      <c r="J296" s="4" t="n"/>
+      <c r="M296" s="4" t="n"/>
     </row>
     <row r="297">
-      <c r="A297" s="3" t="n"/>
+      <c r="A297" s="4" t="n"/>
+      <c r="J297" s="4" t="n"/>
+      <c r="M297" s="4" t="n"/>
     </row>
     <row r="298">
-      <c r="A298" s="3" t="n"/>
+      <c r="A298" s="4" t="n"/>
+      <c r="J298" s="4" t="n"/>
+      <c r="M298" s="4" t="n"/>
     </row>
     <row r="299">
-      <c r="A299" s="3" t="n"/>
+      <c r="A299" s="4" t="n"/>
+      <c r="J299" s="4" t="n"/>
+      <c r="M299" s="4" t="n"/>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="n"/>
+      <c r="A300" s="4" t="n"/>
+      <c r="J300" s="4" t="n"/>
+      <c r="M300" s="4" t="n"/>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="n"/>
+      <c r="A301" s="4" t="n"/>
+      <c r="J301" s="4" t="n"/>
+      <c r="M301" s="4" t="n"/>
     </row>
     <row r="302">
-      <c r="A302" s="3" t="n"/>
+      <c r="A302" s="4" t="n"/>
+      <c r="J302" s="4" t="n"/>
+      <c r="M302" s="4" t="n"/>
     </row>
     <row r="303">
-      <c r="A303" s="3" t="n"/>
+      <c r="A303" s="4" t="n"/>
+      <c r="J303" s="4" t="n"/>
+      <c r="M303" s="4" t="n"/>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="n"/>
+      <c r="A304" s="4" t="n"/>
+      <c r="J304" s="4" t="n"/>
+      <c r="M304" s="4" t="n"/>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="n"/>
+      <c r="A305" s="4" t="n"/>
+      <c r="J305" s="4" t="n"/>
+      <c r="M305" s="4" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="3" t="n"/>
+      <c r="A306" s="4" t="n"/>
+      <c r="J306" s="4" t="n"/>
+      <c r="M306" s="4" t="n"/>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="n"/>
+      <c r="A307" s="4" t="n"/>
+      <c r="J307" s="4" t="n"/>
+      <c r="M307" s="4" t="n"/>
     </row>
     <row r="308">
-      <c r="A308" s="3" t="n"/>
+      <c r="A308" s="4" t="n"/>
+      <c r="J308" s="4" t="n"/>
+      <c r="M308" s="4" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="n"/>
+      <c r="A309" s="4" t="n"/>
+      <c r="J309" s="4" t="n"/>
+      <c r="M309" s="4" t="n"/>
     </row>
     <row r="310">
-      <c r="A310" s="3" t="n"/>
+      <c r="A310" s="4" t="n"/>
+      <c r="J310" s="4" t="n"/>
+      <c r="M310" s="4" t="n"/>
     </row>
     <row r="311">
-      <c r="A311" s="3" t="n"/>
+      <c r="A311" s="4" t="n"/>
+      <c r="J311" s="4" t="n"/>
+      <c r="M311" s="4" t="n"/>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="n"/>
+      <c r="A312" s="4" t="n"/>
+      <c r="J312" s="4" t="n"/>
+      <c r="M312" s="4" t="n"/>
     </row>
     <row r="313">
-      <c r="A313" s="3" t="n"/>
+      <c r="A313" s="4" t="n"/>
+      <c r="J313" s="4" t="n"/>
+      <c r="M313" s="4" t="n"/>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="n"/>
+      <c r="A314" s="4" t="n"/>
+      <c r="J314" s="4" t="n"/>
+      <c r="M314" s="4" t="n"/>
     </row>
     <row r="315">
-      <c r="A315" s="3" t="n"/>
+      <c r="A315" s="4" t="n"/>
+      <c r="J315" s="4" t="n"/>
+      <c r="M315" s="4" t="n"/>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="n"/>
+      <c r="A316" s="4" t="n"/>
+      <c r="J316" s="4" t="n"/>
+      <c r="M316" s="4" t="n"/>
     </row>
     <row r="317">
-      <c r="A317" s="3" t="n"/>
+      <c r="A317" s="4" t="n"/>
+      <c r="J317" s="4" t="n"/>
+      <c r="M317" s="4" t="n"/>
     </row>
     <row r="318">
-      <c r="A318" s="3" t="n"/>
+      <c r="A318" s="4" t="n"/>
+      <c r="J318" s="4" t="n"/>
+      <c r="M318" s="4" t="n"/>
     </row>
     <row r="319">
-      <c r="A319" s="3" t="n"/>
+      <c r="A319" s="4" t="n"/>
+      <c r="J319" s="4" t="n"/>
+      <c r="M319" s="4" t="n"/>
     </row>
     <row r="320">
-      <c r="A320" s="3" t="n"/>
+      <c r="A320" s="4" t="n"/>
+      <c r="J320" s="4" t="n"/>
+      <c r="M320" s="4" t="n"/>
     </row>
     <row r="321">
-      <c r="A321" s="3" t="n"/>
+      <c r="A321" s="4" t="n"/>
+      <c r="J321" s="4" t="n"/>
+      <c r="M321" s="4" t="n"/>
     </row>
     <row r="322">
-      <c r="A322" s="3" t="n"/>
+      <c r="A322" s="4" t="n"/>
+      <c r="J322" s="4" t="n"/>
+      <c r="M322" s="4" t="n"/>
     </row>
     <row r="323">
-      <c r="A323" s="3" t="n"/>
+      <c r="A323" s="4" t="n"/>
+      <c r="J323" s="4" t="n"/>
+      <c r="M323" s="4" t="n"/>
     </row>
     <row r="324">
-      <c r="A324" s="3" t="n"/>
+      <c r="A324" s="4" t="n"/>
+      <c r="J324" s="4" t="n"/>
+      <c r="M324" s="4" t="n"/>
     </row>
     <row r="325">
-      <c r="A325" s="3" t="n"/>
+      <c r="A325" s="4" t="n"/>
+      <c r="J325" s="4" t="n"/>
+      <c r="M325" s="4" t="n"/>
     </row>
     <row r="326">
-      <c r="A326" s="3" t="n"/>
+      <c r="A326" s="4" t="n"/>
+      <c r="J326" s="4" t="n"/>
+      <c r="M326" s="4" t="n"/>
     </row>
     <row r="327">
-      <c r="A327" s="3" t="n"/>
+      <c r="A327" s="4" t="n"/>
+      <c r="J327" s="4" t="n"/>
+      <c r="M327" s="4" t="n"/>
     </row>
     <row r="328">
-      <c r="A328" s="3" t="n"/>
+      <c r="A328" s="4" t="n"/>
+      <c r="J328" s="4" t="n"/>
+      <c r="M328" s="4" t="n"/>
     </row>
     <row r="329">
-      <c r="A329" s="3" t="n"/>
+      <c r="A329" s="4" t="n"/>
+      <c r="J329" s="4" t="n"/>
+      <c r="M329" s="4" t="n"/>
     </row>
     <row r="330">
-      <c r="A330" s="3" t="n"/>
+      <c r="A330" s="4" t="n"/>
+      <c r="J330" s="4" t="n"/>
+      <c r="M330" s="4" t="n"/>
     </row>
     <row r="331">
-      <c r="A331" s="3" t="n"/>
+      <c r="A331" s="4" t="n"/>
+      <c r="J331" s="4" t="n"/>
+      <c r="M331" s="4" t="n"/>
     </row>
     <row r="332">
-      <c r="A332" s="3" t="n"/>
+      <c r="A332" s="4" t="n"/>
+      <c r="J332" s="4" t="n"/>
+      <c r="M332" s="4" t="n"/>
     </row>
     <row r="333">
-      <c r="A333" s="3" t="n"/>
+      <c r="A333" s="4" t="n"/>
+      <c r="J333" s="4" t="n"/>
+      <c r="M333" s="4" t="n"/>
     </row>
     <row r="334">
-      <c r="A334" s="3" t="n"/>
+      <c r="A334" s="4" t="n"/>
+      <c r="J334" s="4" t="n"/>
+      <c r="M334" s="4" t="n"/>
     </row>
     <row r="335">
-      <c r="A335" s="3" t="n"/>
+      <c r="A335" s="4" t="n"/>
+      <c r="J335" s="4" t="n"/>
+      <c r="M335" s="4" t="n"/>
     </row>
     <row r="336">
-      <c r="A336" s="3" t="n"/>
+      <c r="A336" s="4" t="n"/>
+      <c r="J336" s="4" t="n"/>
+      <c r="M336" s="4" t="n"/>
     </row>
     <row r="337">
-      <c r="A337" s="3" t="n"/>
+      <c r="A337" s="4" t="n"/>
+      <c r="J337" s="4" t="n"/>
+      <c r="M337" s="4" t="n"/>
     </row>
     <row r="338">
-      <c r="A338" s="3" t="n"/>
+      <c r="A338" s="4" t="n"/>
+      <c r="J338" s="4" t="n"/>
+      <c r="M338" s="4" t="n"/>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="n"/>
+      <c r="A339" s="4" t="n"/>
+      <c r="J339" s="4" t="n"/>
+      <c r="M339" s="4" t="n"/>
     </row>
     <row r="340">
-      <c r="A340" s="3" t="n"/>
+      <c r="A340" s="4" t="n"/>
+      <c r="J340" s="4" t="n"/>
+      <c r="M340" s="4" t="n"/>
     </row>
     <row r="341">
-      <c r="A341" s="3" t="n"/>
+      <c r="A341" s="4" t="n"/>
+      <c r="J341" s="4" t="n"/>
+      <c r="M341" s="4" t="n"/>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="n"/>
+      <c r="A342" s="4" t="n"/>
+      <c r="J342" s="4" t="n"/>
+      <c r="M342" s="4" t="n"/>
     </row>
     <row r="343">
-      <c r="A343" s="3" t="n"/>
+      <c r="A343" s="4" t="n"/>
+      <c r="J343" s="4" t="n"/>
+      <c r="M343" s="4" t="n"/>
     </row>
     <row r="344">
-      <c r="A344" s="3" t="n"/>
+      <c r="A344" s="4" t="n"/>
+      <c r="J344" s="4" t="n"/>
+      <c r="M344" s="4" t="n"/>
     </row>
     <row r="345">
-      <c r="A345" s="3" t="n"/>
+      <c r="A345" s="4" t="n"/>
+      <c r="J345" s="4" t="n"/>
+      <c r="M345" s="4" t="n"/>
     </row>
     <row r="346">
-      <c r="A346" s="3" t="n"/>
+      <c r="A346" s="4" t="n"/>
+      <c r="J346" s="4" t="n"/>
+      <c r="M346" s="4" t="n"/>
     </row>
     <row r="347">
-      <c r="A347" s="3" t="n"/>
+      <c r="A347" s="4" t="n"/>
+      <c r="J347" s="4" t="n"/>
+      <c r="M347" s="4" t="n"/>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="n"/>
+      <c r="A348" s="4" t="n"/>
+      <c r="J348" s="4" t="n"/>
+      <c r="M348" s="4" t="n"/>
     </row>
     <row r="349">
-      <c r="A349" s="3" t="n"/>
+      <c r="A349" s="4" t="n"/>
+      <c r="J349" s="4" t="n"/>
+      <c r="M349" s="4" t="n"/>
     </row>
     <row r="350">
-      <c r="A350" s="3" t="n"/>
+      <c r="A350" s="4" t="n"/>
+      <c r="J350" s="4" t="n"/>
+      <c r="M350" s="4" t="n"/>
     </row>
     <row r="351">
-      <c r="A351" s="3" t="n"/>
+      <c r="A351" s="4" t="n"/>
+      <c r="J351" s="4" t="n"/>
+      <c r="M351" s="4" t="n"/>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="n"/>
+      <c r="A352" s="4" t="n"/>
+      <c r="J352" s="4" t="n"/>
+      <c r="M352" s="4" t="n"/>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="n"/>
+      <c r="A353" s="4" t="n"/>
+      <c r="J353" s="4" t="n"/>
+      <c r="M353" s="4" t="n"/>
     </row>
     <row r="354">
-      <c r="A354" s="3" t="n"/>
+      <c r="A354" s="4" t="n"/>
+      <c r="J354" s="4" t="n"/>
+      <c r="M354" s="4" t="n"/>
     </row>
     <row r="355">
-      <c r="A355" s="3" t="n"/>
+      <c r="A355" s="4" t="n"/>
+      <c r="J355" s="4" t="n"/>
+      <c r="M355" s="4" t="n"/>
     </row>
     <row r="356">
-      <c r="A356" s="3" t="n"/>
+      <c r="A356" s="4" t="n"/>
+      <c r="J356" s="4" t="n"/>
+      <c r="M356" s="4" t="n"/>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="n"/>
+      <c r="A357" s="4" t="n"/>
+      <c r="J357" s="4" t="n"/>
+      <c r="M357" s="4" t="n"/>
     </row>
     <row r="358">
-      <c r="A358" s="3" t="n"/>
+      <c r="A358" s="4" t="n"/>
+      <c r="J358" s="4" t="n"/>
+      <c r="M358" s="4" t="n"/>
     </row>
     <row r="359">
-      <c r="A359" s="3" t="n"/>
+      <c r="A359" s="4" t="n"/>
+      <c r="J359" s="4" t="n"/>
+      <c r="M359" s="4" t="n"/>
     </row>
     <row r="360">
-      <c r="A360" s="3" t="n"/>
+      <c r="A360" s="4" t="n"/>
+      <c r="J360" s="4" t="n"/>
+      <c r="M360" s="4" t="n"/>
     </row>
     <row r="361">
-      <c r="A361" s="3" t="n"/>
+      <c r="A361" s="4" t="n"/>
+      <c r="J361" s="4" t="n"/>
+      <c r="M361" s="4" t="n"/>
     </row>
     <row r="362">
-      <c r="A362" s="3" t="n"/>
+      <c r="A362" s="4" t="n"/>
+      <c r="J362" s="4" t="n"/>
+      <c r="M362" s="4" t="n"/>
     </row>
     <row r="363">
-      <c r="A363" s="3" t="n"/>
+      <c r="A363" s="4" t="n"/>
+      <c r="J363" s="4" t="n"/>
+      <c r="M363" s="4" t="n"/>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="n"/>
+      <c r="A364" s="4" t="n"/>
+      <c r="J364" s="4" t="n"/>
+      <c r="M364" s="4" t="n"/>
     </row>
     <row r="365">
-      <c r="A365" s="3" t="n"/>
+      <c r="A365" s="4" t="n"/>
+      <c r="J365" s="4" t="n"/>
+      <c r="M365" s="4" t="n"/>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="n"/>
+      <c r="A366" s="4" t="n"/>
+      <c r="J366" s="4" t="n"/>
+      <c r="M366" s="4" t="n"/>
     </row>
     <row r="367">
-      <c r="A367" s="3" t="n"/>
+      <c r="A367" s="4" t="n"/>
+      <c r="J367" s="4" t="n"/>
+      <c r="M367" s="4" t="n"/>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="n"/>
+      <c r="A368" s="4" t="n"/>
+      <c r="J368" s="4" t="n"/>
+      <c r="M368" s="4" t="n"/>
     </row>
     <row r="369">
-      <c r="A369" s="3" t="n"/>
+      <c r="A369" s="4" t="n"/>
+      <c r="J369" s="4" t="n"/>
+      <c r="M369" s="4" t="n"/>
     </row>
     <row r="370">
-      <c r="A370" s="3" t="n"/>
+      <c r="A370" s="4" t="n"/>
+      <c r="J370" s="4" t="n"/>
+      <c r="M370" s="4" t="n"/>
     </row>
     <row r="371">
-      <c r="A371" s="3" t="n"/>
+      <c r="A371" s="4" t="n"/>
+      <c r="J371" s="4" t="n"/>
+      <c r="M371" s="4" t="n"/>
     </row>
     <row r="372">
-      <c r="A372" s="3" t="n"/>
+      <c r="A372" s="4" t="n"/>
+      <c r="J372" s="4" t="n"/>
+      <c r="M372" s="4" t="n"/>
     </row>
     <row r="373">
-      <c r="A373" s="3" t="n"/>
+      <c r="A373" s="4" t="n"/>
+      <c r="J373" s="4" t="n"/>
+      <c r="M373" s="4" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="3" t="n"/>
+      <c r="A374" s="4" t="n"/>
+      <c r="J374" s="4" t="n"/>
+      <c r="M374" s="4" t="n"/>
     </row>
     <row r="375">
-      <c r="A375" s="3" t="n"/>
+      <c r="A375" s="4" t="n"/>
+      <c r="J375" s="4" t="n"/>
+      <c r="M375" s="4" t="n"/>
     </row>
     <row r="376">
-      <c r="A376" s="3" t="n"/>
+      <c r="A376" s="4" t="n"/>
+      <c r="J376" s="4" t="n"/>
+      <c r="M376" s="4" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="n"/>
+      <c r="A377" s="4" t="n"/>
+      <c r="J377" s="4" t="n"/>
+      <c r="M377" s="4" t="n"/>
     </row>
     <row r="378">
-      <c r="A378" s="3" t="n"/>
+      <c r="A378" s="4" t="n"/>
+      <c r="J378" s="4" t="n"/>
+      <c r="M378" s="4" t="n"/>
     </row>
     <row r="379">
-      <c r="A379" s="3" t="n"/>
+      <c r="A379" s="4" t="n"/>
+      <c r="J379" s="4" t="n"/>
+      <c r="M379" s="4" t="n"/>
     </row>
     <row r="380">
-      <c r="A380" s="3" t="n"/>
+      <c r="A380" s="4" t="n"/>
+      <c r="J380" s="4" t="n"/>
+      <c r="M380" s="4" t="n"/>
     </row>
     <row r="381">
-      <c r="A381" s="3" t="n"/>
+      <c r="A381" s="4" t="n"/>
+      <c r="J381" s="4" t="n"/>
+      <c r="M381" s="4" t="n"/>
     </row>
     <row r="382">
-      <c r="A382" s="3" t="n"/>
+      <c r="A382" s="4" t="n"/>
+      <c r="J382" s="4" t="n"/>
+      <c r="M382" s="4" t="n"/>
     </row>
     <row r="383">
-      <c r="A383" s="3" t="n"/>
+      <c r="A383" s="4" t="n"/>
+      <c r="J383" s="4" t="n"/>
+      <c r="M383" s="4" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="3" t="n"/>
+      <c r="A384" s="4" t="n"/>
+      <c r="J384" s="4" t="n"/>
+      <c r="M384" s="4" t="n"/>
     </row>
     <row r="385">
-      <c r="A385" s="3" t="n"/>
+      <c r="A385" s="4" t="n"/>
+      <c r="J385" s="4" t="n"/>
+      <c r="M385" s="4" t="n"/>
     </row>
     <row r="386">
-      <c r="A386" s="3" t="n"/>
+      <c r="A386" s="4" t="n"/>
+      <c r="J386" s="4" t="n"/>
+      <c r="M386" s="4" t="n"/>
     </row>
     <row r="387">
-      <c r="A387" s="3" t="n"/>
+      <c r="A387" s="4" t="n"/>
+      <c r="J387" s="4" t="n"/>
+      <c r="M387" s="4" t="n"/>
     </row>
     <row r="388">
-      <c r="A388" s="3" t="n"/>
+      <c r="A388" s="4" t="n"/>
+      <c r="J388" s="4" t="n"/>
+      <c r="M388" s="4" t="n"/>
     </row>
     <row r="389">
-      <c r="A389" s="3" t="n"/>
+      <c r="A389" s="4" t="n"/>
+      <c r="J389" s="4" t="n"/>
+      <c r="M389" s="4" t="n"/>
     </row>
     <row r="390">
-      <c r="A390" s="3" t="n"/>
+      <c r="A390" s="4" t="n"/>
+      <c r="J390" s="4" t="n"/>
+      <c r="M390" s="4" t="n"/>
     </row>
     <row r="391">
-      <c r="A391" s="3" t="n"/>
+      <c r="A391" s="4" t="n"/>
+      <c r="J391" s="4" t="n"/>
+      <c r="M391" s="4" t="n"/>
     </row>
     <row r="392">
-      <c r="A392" s="3" t="n"/>
+      <c r="A392" s="4" t="n"/>
+      <c r="J392" s="4" t="n"/>
+      <c r="M392" s="4" t="n"/>
     </row>
     <row r="393">
-      <c r="A393" s="3" t="n"/>
+      <c r="A393" s="4" t="n"/>
+      <c r="J393" s="4" t="n"/>
+      <c r="M393" s="4" t="n"/>
     </row>
     <row r="394">
-      <c r="A394" s="3" t="n"/>
+      <c r="A394" s="4" t="n"/>
+      <c r="J394" s="4" t="n"/>
+      <c r="M394" s="4" t="n"/>
     </row>
     <row r="395">
-      <c r="A395" s="3" t="n"/>
+      <c r="A395" s="4" t="n"/>
+      <c r="J395" s="4" t="n"/>
+      <c r="M395" s="4" t="n"/>
     </row>
     <row r="396">
-      <c r="A396" s="3" t="n"/>
+      <c r="A396" s="4" t="n"/>
+      <c r="J396" s="4" t="n"/>
+      <c r="M396" s="4" t="n"/>
     </row>
     <row r="397">
-      <c r="A397" s="3" t="n"/>
+      <c r="A397" s="4" t="n"/>
+      <c r="J397" s="4" t="n"/>
+      <c r="M397" s="4" t="n"/>
     </row>
     <row r="398">
-      <c r="A398" s="3" t="n"/>
+      <c r="A398" s="4" t="n"/>
+      <c r="J398" s="4" t="n"/>
+      <c r="M398" s="4" t="n"/>
     </row>
     <row r="399">
-      <c r="A399" s="3" t="n"/>
+      <c r="A399" s="4" t="n"/>
+      <c r="J399" s="4" t="n"/>
+      <c r="M399" s="4" t="n"/>
     </row>
     <row r="400">
-      <c r="A400" s="3" t="n"/>
+      <c r="A400" s="4" t="n"/>
+      <c r="J400" s="4" t="n"/>
+      <c r="M400" s="4" t="n"/>
     </row>
     <row r="401">
-      <c r="A401" s="3" t="n"/>
+      <c r="A401" s="4" t="n"/>
+      <c r="J401" s="4" t="n"/>
+      <c r="M401" s="4" t="n"/>
     </row>
     <row r="402">
-      <c r="A402" s="3" t="n"/>
+      <c r="A402" s="4" t="n"/>
+      <c r="J402" s="4" t="n"/>
+      <c r="M402" s="4" t="n"/>
     </row>
     <row r="403">
-      <c r="A403" s="3" t="n"/>
+      <c r="A403" s="4" t="n"/>
+      <c r="J403" s="4" t="n"/>
+      <c r="M403" s="4" t="n"/>
     </row>
     <row r="404">
-      <c r="A404" s="3" t="n"/>
+      <c r="A404" s="4" t="n"/>
+      <c r="J404" s="4" t="n"/>
+      <c r="M404" s="4" t="n"/>
     </row>
     <row r="405">
-      <c r="A405" s="3" t="n"/>
+      <c r="A405" s="4" t="n"/>
+      <c r="J405" s="4" t="n"/>
+      <c r="M405" s="4" t="n"/>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="n"/>
+      <c r="A406" s="4" t="n"/>
+      <c r="J406" s="4" t="n"/>
+      <c r="M406" s="4" t="n"/>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="n"/>
+      <c r="A407" s="4" t="n"/>
+      <c r="J407" s="4" t="n"/>
+      <c r="M407" s="4" t="n"/>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="n"/>
+      <c r="A408" s="4" t="n"/>
+      <c r="J408" s="4" t="n"/>
+      <c r="M408" s="4" t="n"/>
     </row>
     <row r="409">
-      <c r="A409" s="3" t="n"/>
+      <c r="A409" s="4" t="n"/>
+      <c r="J409" s="4" t="n"/>
+      <c r="M409" s="4" t="n"/>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="n"/>
+      <c r="A410" s="4" t="n"/>
+      <c r="J410" s="4" t="n"/>
+      <c r="M410" s="4" t="n"/>
     </row>
     <row r="411">
-      <c r="A411" s="3" t="n"/>
+      <c r="A411" s="4" t="n"/>
+      <c r="J411" s="4" t="n"/>
+      <c r="M411" s="4" t="n"/>
     </row>
     <row r="412">
-      <c r="A412" s="3" t="n"/>
+      <c r="A412" s="4" t="n"/>
+      <c r="J412" s="4" t="n"/>
+      <c r="M412" s="4" t="n"/>
     </row>
     <row r="413">
-      <c r="A413" s="3" t="n"/>
+      <c r="A413" s="4" t="n"/>
+      <c r="J413" s="4" t="n"/>
+      <c r="M413" s="4" t="n"/>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="n"/>
+      <c r="A414" s="4" t="n"/>
+      <c r="J414" s="4" t="n"/>
+      <c r="M414" s="4" t="n"/>
     </row>
     <row r="415">
-      <c r="A415" s="3" t="n"/>
+      <c r="A415" s="4" t="n"/>
+      <c r="J415" s="4" t="n"/>
+      <c r="M415" s="4" t="n"/>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="n"/>
+      <c r="A416" s="4" t="n"/>
+      <c r="J416" s="4" t="n"/>
+      <c r="M416" s="4" t="n"/>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="n"/>
+      <c r="A417" s="4" t="n"/>
+      <c r="J417" s="4" t="n"/>
+      <c r="M417" s="4" t="n"/>
     </row>
     <row r="418">
-      <c r="A418" s="3" t="n"/>
+      <c r="A418" s="4" t="n"/>
+      <c r="J418" s="4" t="n"/>
+      <c r="M418" s="4" t="n"/>
     </row>
     <row r="419">
-      <c r="A419" s="3" t="n"/>
+      <c r="A419" s="4" t="n"/>
+      <c r="J419" s="4" t="n"/>
+      <c r="M419" s="4" t="n"/>
     </row>
     <row r="420">
-      <c r="A420" s="3" t="n"/>
+      <c r="A420" s="4" t="n"/>
+      <c r="J420" s="4" t="n"/>
+      <c r="M420" s="4" t="n"/>
     </row>
     <row r="421">
-      <c r="A421" s="3" t="n"/>
+      <c r="A421" s="4" t="n"/>
+      <c r="J421" s="4" t="n"/>
+      <c r="M421" s="4" t="n"/>
     </row>
     <row r="422">
-      <c r="A422" s="3" t="n"/>
+      <c r="A422" s="4" t="n"/>
+      <c r="J422" s="4" t="n"/>
+      <c r="M422" s="4" t="n"/>
     </row>
     <row r="423">
-      <c r="A423" s="3" t="n"/>
+      <c r="A423" s="4" t="n"/>
+      <c r="J423" s="4" t="n"/>
+      <c r="M423" s="4" t="n"/>
     </row>
     <row r="424">
-      <c r="A424" s="3" t="n"/>
+      <c r="A424" s="4" t="n"/>
+      <c r="J424" s="4" t="n"/>
+      <c r="M424" s="4" t="n"/>
     </row>
     <row r="425">
-      <c r="A425" s="3" t="n"/>
+      <c r="A425" s="4" t="n"/>
+      <c r="J425" s="4" t="n"/>
+      <c r="M425" s="4" t="n"/>
     </row>
     <row r="426">
-      <c r="A426" s="3" t="n"/>
+      <c r="A426" s="4" t="n"/>
+      <c r="J426" s="4" t="n"/>
+      <c r="M426" s="4" t="n"/>
     </row>
     <row r="427">
-      <c r="A427" s="3" t="n"/>
+      <c r="A427" s="4" t="n"/>
+      <c r="J427" s="4" t="n"/>
+      <c r="M427" s="4" t="n"/>
     </row>
     <row r="428">
-      <c r="A428" s="3" t="n"/>
+      <c r="A428" s="4" t="n"/>
+      <c r="J428" s="4" t="n"/>
+      <c r="M428" s="4" t="n"/>
     </row>
     <row r="429">
-      <c r="A429" s="3" t="n"/>
+      <c r="A429" s="4" t="n"/>
+      <c r="J429" s="4" t="n"/>
+      <c r="M429" s="4" t="n"/>
     </row>
     <row r="430">
-      <c r="A430" s="3" t="n"/>
+      <c r="A430" s="4" t="n"/>
+      <c r="J430" s="4" t="n"/>
+      <c r="M430" s="4" t="n"/>
     </row>
     <row r="431">
-      <c r="A431" s="3" t="n"/>
+      <c r="A431" s="4" t="n"/>
+      <c r="J431" s="4" t="n"/>
+      <c r="M431" s="4" t="n"/>
     </row>
     <row r="432">
-      <c r="A432" s="3" t="n"/>
+      <c r="A432" s="4" t="n"/>
+      <c r="J432" s="4" t="n"/>
+      <c r="M432" s="4" t="n"/>
     </row>
     <row r="433">
-      <c r="A433" s="3" t="n"/>
+      <c r="A433" s="4" t="n"/>
+      <c r="J433" s="4" t="n"/>
+      <c r="M433" s="4" t="n"/>
     </row>
     <row r="434">
-      <c r="A434" s="3" t="n"/>
+      <c r="A434" s="4" t="n"/>
+      <c r="J434" s="4" t="n"/>
+      <c r="M434" s="4" t="n"/>
     </row>
     <row r="435">
-      <c r="A435" s="3" t="n"/>
+      <c r="A435" s="4" t="n"/>
+      <c r="J435" s="4" t="n"/>
+      <c r="M435" s="4" t="n"/>
     </row>
     <row r="436">
-      <c r="A436" s="3" t="n"/>
+      <c r="A436" s="4" t="n"/>
+      <c r="J436" s="4" t="n"/>
+      <c r="M436" s="4" t="n"/>
     </row>
     <row r="437">
-      <c r="A437" s="3" t="n"/>
+      <c r="A437" s="4" t="n"/>
+      <c r="J437" s="4" t="n"/>
+      <c r="M437" s="4" t="n"/>
     </row>
     <row r="438">
-      <c r="A438" s="3" t="n"/>
+      <c r="A438" s="4" t="n"/>
+      <c r="J438" s="4" t="n"/>
+      <c r="M438" s="4" t="n"/>
     </row>
     <row r="439">
-      <c r="A439" s="3" t="n"/>
+      <c r="A439" s="4" t="n"/>
+      <c r="J439" s="4" t="n"/>
+      <c r="M439" s="4" t="n"/>
     </row>
     <row r="440">
-      <c r="A440" s="3" t="n"/>
+      <c r="A440" s="4" t="n"/>
+      <c r="J440" s="4" t="n"/>
+      <c r="M440" s="4" t="n"/>
     </row>
     <row r="441">
-      <c r="A441" s="3" t="n"/>
+      <c r="A441" s="4" t="n"/>
+      <c r="J441" s="4" t="n"/>
+      <c r="M441" s="4" t="n"/>
     </row>
     <row r="442">
-      <c r="A442" s="3" t="n"/>
+      <c r="A442" s="4" t="n"/>
+      <c r="J442" s="4" t="n"/>
+      <c r="M442" s="4" t="n"/>
     </row>
     <row r="443">
-      <c r="A443" s="3" t="n"/>
+      <c r="A443" s="4" t="n"/>
+      <c r="J443" s="4" t="n"/>
+      <c r="M443" s="4" t="n"/>
     </row>
     <row r="444">
-      <c r="A444" s="3" t="n"/>
+      <c r="A444" s="4" t="n"/>
+      <c r="J444" s="4" t="n"/>
+      <c r="M444" s="4" t="n"/>
     </row>
     <row r="445">
-      <c r="A445" s="3" t="n"/>
+      <c r="A445" s="4" t="n"/>
+      <c r="J445" s="4" t="n"/>
+      <c r="M445" s="4" t="n"/>
     </row>
     <row r="446">
-      <c r="A446" s="3" t="n"/>
+      <c r="A446" s="4" t="n"/>
+      <c r="J446" s="4" t="n"/>
+      <c r="M446" s="4" t="n"/>
     </row>
     <row r="447">
-      <c r="A447" s="3" t="n"/>
+      <c r="A447" s="4" t="n"/>
+      <c r="J447" s="4" t="n"/>
+      <c r="M447" s="4" t="n"/>
     </row>
     <row r="448">
-      <c r="A448" s="3" t="n"/>
+      <c r="A448" s="4" t="n"/>
+      <c r="J448" s="4" t="n"/>
+      <c r="M448" s="4" t="n"/>
     </row>
     <row r="449">
-      <c r="A449" s="3" t="n"/>
+      <c r="A449" s="4" t="n"/>
+      <c r="J449" s="4" t="n"/>
+      <c r="M449" s="4" t="n"/>
     </row>
     <row r="450">
-      <c r="A450" s="3" t="n"/>
+      <c r="A450" s="4" t="n"/>
+      <c r="J450" s="4" t="n"/>
+      <c r="M450" s="4" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="3" t="n"/>
+      <c r="A451" s="4" t="n"/>
+      <c r="J451" s="4" t="n"/>
+      <c r="M451" s="4" t="n"/>
     </row>
     <row r="452">
-      <c r="A452" s="3" t="n"/>
+      <c r="A452" s="4" t="n"/>
+      <c r="J452" s="4" t="n"/>
+      <c r="M452" s="4" t="n"/>
     </row>
     <row r="453">
-      <c r="A453" s="3" t="n"/>
+      <c r="A453" s="4" t="n"/>
+      <c r="J453" s="4" t="n"/>
+      <c r="M453" s="4" t="n"/>
     </row>
     <row r="454">
-      <c r="A454" s="3" t="n"/>
+      <c r="A454" s="4" t="n"/>
+      <c r="J454" s="4" t="n"/>
+      <c r="M454" s="4" t="n"/>
     </row>
     <row r="455">
-      <c r="A455" s="3" t="n"/>
+      <c r="A455" s="4" t="n"/>
+      <c r="J455" s="4" t="n"/>
+      <c r="M455" s="4" t="n"/>
     </row>
     <row r="456">
-      <c r="A456" s="3" t="n"/>
+      <c r="A456" s="4" t="n"/>
+      <c r="J456" s="4" t="n"/>
+      <c r="M456" s="4" t="n"/>
     </row>
     <row r="457">
-      <c r="A457" s="3" t="n"/>
+      <c r="A457" s="4" t="n"/>
+      <c r="J457" s="4" t="n"/>
+      <c r="M457" s="4" t="n"/>
     </row>
     <row r="458">
-      <c r="A458" s="3" t="n"/>
+      <c r="A458" s="4" t="n"/>
+      <c r="J458" s="4" t="n"/>
+      <c r="M458" s="4" t="n"/>
     </row>
     <row r="459">
-      <c r="A459" s="3" t="n"/>
+      <c r="A459" s="4" t="n"/>
+      <c r="J459" s="4" t="n"/>
+      <c r="M459" s="4" t="n"/>
     </row>
     <row r="460">
-      <c r="A460" s="3" t="n"/>
+      <c r="A460" s="4" t="n"/>
+      <c r="J460" s="4" t="n"/>
+      <c r="M460" s="4" t="n"/>
     </row>
     <row r="461">
-      <c r="A461" s="3" t="n"/>
+      <c r="A461" s="4" t="n"/>
+      <c r="J461" s="4" t="n"/>
+      <c r="M461" s="4" t="n"/>
     </row>
     <row r="462">
-      <c r="A462" s="3" t="n"/>
+      <c r="A462" s="4" t="n"/>
+      <c r="J462" s="4" t="n"/>
+      <c r="M462" s="4" t="n"/>
     </row>
     <row r="463">
-      <c r="A463" s="3" t="n"/>
+      <c r="A463" s="4" t="n"/>
+      <c r="J463" s="4" t="n"/>
+      <c r="M463" s="4" t="n"/>
     </row>
     <row r="464">
-      <c r="A464" s="3" t="n"/>
+      <c r="A464" s="4" t="n"/>
+      <c r="J464" s="4" t="n"/>
+      <c r="M464" s="4" t="n"/>
     </row>
     <row r="465">
-      <c r="A465" s="3" t="n"/>
+      <c r="A465" s="4" t="n"/>
+      <c r="J465" s="4" t="n"/>
+      <c r="M465" s="4" t="n"/>
     </row>
     <row r="466">
-      <c r="A466" s="3" t="n"/>
+      <c r="A466" s="4" t="n"/>
+      <c r="J466" s="4" t="n"/>
+      <c r="M466" s="4" t="n"/>
     </row>
     <row r="467">
-      <c r="A467" s="3" t="n"/>
+      <c r="A467" s="4" t="n"/>
+      <c r="J467" s="4" t="n"/>
+      <c r="M467" s="4" t="n"/>
     </row>
     <row r="468">
-      <c r="A468" s="3" t="n"/>
+      <c r="A468" s="4" t="n"/>
+      <c r="J468" s="4" t="n"/>
+      <c r="M468" s="4" t="n"/>
     </row>
     <row r="469">
-      <c r="A469" s="3" t="n"/>
+      <c r="A469" s="4" t="n"/>
+      <c r="J469" s="4" t="n"/>
+      <c r="M469" s="4" t="n"/>
     </row>
     <row r="470">
-      <c r="A470" s="3" t="n"/>
+      <c r="A470" s="4" t="n"/>
+      <c r="J470" s="4" t="n"/>
+      <c r="M470" s="4" t="n"/>
     </row>
     <row r="471">
-      <c r="A471" s="3" t="n"/>
+      <c r="A471" s="4" t="n"/>
+      <c r="J471" s="4" t="n"/>
+      <c r="M471" s="4" t="n"/>
     </row>
     <row r="472">
-      <c r="A472" s="3" t="n"/>
+      <c r="A472" s="4" t="n"/>
+      <c r="J472" s="4" t="n"/>
+      <c r="M472" s="4" t="n"/>
     </row>
     <row r="473">
-      <c r="A473" s="3" t="n"/>
+      <c r="A473" s="4" t="n"/>
+      <c r="J473" s="4" t="n"/>
+      <c r="M473" s="4" t="n"/>
     </row>
     <row r="474">
-      <c r="A474" s="3" t="n"/>
+      <c r="A474" s="4" t="n"/>
+      <c r="J474" s="4" t="n"/>
+      <c r="M474" s="4" t="n"/>
     </row>
     <row r="475">
-      <c r="A475" s="3" t="n"/>
+      <c r="A475" s="4" t="n"/>
+      <c r="J475" s="4" t="n"/>
+      <c r="M475" s="4" t="n"/>
     </row>
     <row r="476">
-      <c r="A476" s="3" t="n"/>
+      <c r="A476" s="4" t="n"/>
+      <c r="J476" s="4" t="n"/>
+      <c r="M476" s="4" t="n"/>
     </row>
     <row r="477">
-      <c r="A477" s="3" t="n"/>
+      <c r="A477" s="4" t="n"/>
+      <c r="J477" s="4" t="n"/>
+      <c r="M477" s="4" t="n"/>
     </row>
     <row r="478">
-      <c r="A478" s="3" t="n"/>
+      <c r="A478" s="4" t="n"/>
+      <c r="J478" s="4" t="n"/>
+      <c r="M478" s="4" t="n"/>
     </row>
     <row r="479">
-      <c r="A479" s="3" t="n"/>
+      <c r="A479" s="4" t="n"/>
+      <c r="J479" s="4" t="n"/>
+      <c r="M479" s="4" t="n"/>
     </row>
     <row r="480">
-      <c r="A480" s="3" t="n"/>
+      <c r="A480" s="4" t="n"/>
+      <c r="J480" s="4" t="n"/>
+      <c r="M480" s="4" t="n"/>
     </row>
     <row r="481">
-      <c r="A481" s="3" t="n"/>
+      <c r="A481" s="4" t="n"/>
+      <c r="J481" s="4" t="n"/>
+      <c r="M481" s="4" t="n"/>
     </row>
     <row r="482">
-      <c r="A482" s="3" t="n"/>
+      <c r="A482" s="4" t="n"/>
+      <c r="J482" s="4" t="n"/>
+      <c r="M482" s="4" t="n"/>
     </row>
     <row r="483">
-      <c r="A483" s="3" t="n"/>
+      <c r="A483" s="4" t="n"/>
+      <c r="J483" s="4" t="n"/>
+      <c r="M483" s="4" t="n"/>
     </row>
     <row r="484">
-      <c r="A484" s="3" t="n"/>
+      <c r="A484" s="4" t="n"/>
+      <c r="J484" s="4" t="n"/>
+      <c r="M484" s="4" t="n"/>
     </row>
     <row r="485">
-      <c r="A485" s="3" t="n"/>
+      <c r="A485" s="4" t="n"/>
+      <c r="J485" s="4" t="n"/>
+      <c r="M485" s="4" t="n"/>
     </row>
     <row r="486">
-      <c r="A486" s="3" t="n"/>
+      <c r="A486" s="4" t="n"/>
+      <c r="J486" s="4" t="n"/>
+      <c r="M486" s="4" t="n"/>
     </row>
     <row r="487">
-      <c r="A487" s="3" t="n"/>
+      <c r="A487" s="4" t="n"/>
+      <c r="J487" s="4" t="n"/>
+      <c r="M487" s="4" t="n"/>
     </row>
     <row r="488">
-      <c r="A488" s="3" t="n"/>
+      <c r="A488" s="4" t="n"/>
+      <c r="J488" s="4" t="n"/>
+      <c r="M488" s="4" t="n"/>
     </row>
     <row r="489">
-      <c r="A489" s="3" t="n"/>
+      <c r="A489" s="4" t="n"/>
+      <c r="J489" s="4" t="n"/>
+      <c r="M489" s="4" t="n"/>
     </row>
     <row r="490">
-      <c r="A490" s="3" t="n"/>
+      <c r="A490" s="4" t="n"/>
+      <c r="J490" s="4" t="n"/>
+      <c r="M490" s="4" t="n"/>
     </row>
     <row r="491">
-      <c r="A491" s="3" t="n"/>
+      <c r="A491" s="4" t="n"/>
+      <c r="J491" s="4" t="n"/>
+      <c r="M491" s="4" t="n"/>
     </row>
     <row r="492">
-      <c r="A492" s="3" t="n"/>
+      <c r="A492" s="4" t="n"/>
+      <c r="J492" s="4" t="n"/>
+      <c r="M492" s="4" t="n"/>
     </row>
     <row r="493">
-      <c r="A493" s="3" t="n"/>
+      <c r="A493" s="4" t="n"/>
+      <c r="J493" s="4" t="n"/>
+      <c r="M493" s="4" t="n"/>
     </row>
     <row r="494">
-      <c r="A494" s="3" t="n"/>
+      <c r="A494" s="4" t="n"/>
+      <c r="J494" s="4" t="n"/>
+      <c r="M494" s="4" t="n"/>
     </row>
     <row r="495">
-      <c r="A495" s="3" t="n"/>
+      <c r="A495" s="4" t="n"/>
+      <c r="J495" s="4" t="n"/>
+      <c r="M495" s="4" t="n"/>
     </row>
     <row r="496">
-      <c r="A496" s="3" t="n"/>
+      <c r="A496" s="4" t="n"/>
+      <c r="J496" s="4" t="n"/>
+      <c r="M496" s="4" t="n"/>
     </row>
     <row r="497">
-      <c r="A497" s="3" t="n"/>
+      <c r="A497" s="4" t="n"/>
+      <c r="J497" s="4" t="n"/>
+      <c r="M497" s="4" t="n"/>
     </row>
     <row r="498">
-      <c r="A498" s="3" t="n"/>
+      <c r="A498" s="4" t="n"/>
+      <c r="J498" s="4" t="n"/>
+      <c r="M498" s="4" t="n"/>
     </row>
     <row r="499">
-      <c r="A499" s="3" t="n"/>
+      <c r="A499" s="4" t="n"/>
+      <c r="J499" s="4" t="n"/>
+      <c r="M499" s="4" t="n"/>
     </row>
     <row r="500">
-      <c r="A500" s="3" t="n"/>
+      <c r="A500" s="4" t="n"/>
+      <c r="J500" s="4" t="n"/>
+      <c r="M500" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J500"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:N500"/>
+  <dataValidations count="5">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$41</formula1>
     </dataValidation>
@@ -2219,6 +3316,13 @@
     </dataValidation>
     <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$B$2:$B$41</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$D$2:$D$41</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>5</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2237,26 +3341,32 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Genres</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Locations</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Formats</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>These lists feed the dropdowns on the My library tab. Edit them to match your shelves.</t>
         </is>
@@ -2278,6 +3388,11 @@
           <t>Hardcover</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2295,6 +3410,11 @@
           <t>Softcover</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Currently reading</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2307,6 +3427,11 @@
           <t>Office</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>To read</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2317,6 +3442,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Hallway</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Did not finish</t>
         </is>
       </c>
     </row>
@@ -2385,42 +3515,49 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Home library inventory</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>1. Add one row per book on the My library tab. The ISBN is on the back cover or the copyright page.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>2. Genre, Format, and Location are dropdowns. Edit the choices on the Lists tab to match your shelves.</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2. Genre, Format, Location, and Status are dropdowns. Edit the choices on the Lists tab to match your shelves.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>3. Keep the header row as it is. Sort and filter from row 2 down.</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>3. The green columns are your reading life: status, rating, when you read it, what you thought.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>4. The example rows show the idea. Replace them with your own books.</t>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>4. Keep the header row as it is. Sort and filter from row 2 down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>5. The example rows show the idea. Replace them with your own books.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Made by Bookplate (bookplate.app). If the spreadsheet ever starts to feel like homework, import this exact file and your covers and book details fill in for you.</t>
         </is>
